--- a/Catch models/bk_macarellus.xlsx
+++ b/Catch models/bk_macarellus.xlsx
@@ -462,7 +462,7 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -477,13 +477,13 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="H2">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -491,7 +491,7 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -506,13 +506,13 @@
         <v>15</v>
       </c>
       <c r="G3">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H3">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="I3">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -549,7 +549,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>

--- a/Catch models/bk_macarellus.xlsx
+++ b/Catch models/bk_macarellus.xlsx
@@ -462,7 +462,7 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -477,13 +477,13 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H2">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="I2">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -491,7 +491,7 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -509,10 +509,10 @@
         <v>0.01</v>
       </c>
       <c r="H3">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="I3">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -535,13 +535,13 @@
         <v>19</v>
       </c>
       <c r="G4">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I4">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -549,7 +549,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>

--- a/Catch models/bk_macarellus.xlsx
+++ b/Catch models/bk_macarellus.xlsx
@@ -509,10 +509,10 @@
         <v>0.01</v>
       </c>
       <c r="H3">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I3">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="4" spans="1:9">
